--- a/public/sap-reporting/expansion-150-downloads/EXT-CO23-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO23-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rd67e848ebf624b08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R025e06fa00884c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb27ddef19a4248f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R80409e6bf55d41b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rff2721d2eadb4c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R97d5f076aeae4d4e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -578,10 +578,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="O8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P8" s="2" t="str"/>
       <x:c r="Q8" s="2" t="str">
@@ -635,10 +635,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="O9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P9" s="2" t="str">
         <x:v>X</x:v>
@@ -694,10 +694,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="O10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P10" s="2" t="str">
         <x:v>X</x:v>
@@ -909,10 +909,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="O3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P3" s="2" t="str"/>
       <x:c r="Q3" s="2" t="str">
@@ -966,10 +966,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="O4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P4" s="2" t="str">
         <x:v>X</x:v>
@@ -1025,10 +1025,10 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="N5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="O5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P5" s="2" t="str">
         <x:v>X</x:v>
@@ -1343,7 +1343,7 @@
         <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="63" customHeight="1">
+    <x:row r="15" ht="80" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>14</x:v>
       </x:c>
@@ -1351,7 +1351,7 @@
         <x:v>Sender Credit</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Sender Credit. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1360,10 +1360,10 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F15" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="63" customHeight="1">
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="80" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -1371,7 +1371,7 @@
         <x:v>Receiver Debit</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Receiver Debit. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1380,7 +1380,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="63" customHeight="1">
